--- a/data/trans_bre/IP1005-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1005-Clase-trans_bre.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>0,0; 3,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,96</t>
+          <t>-2,84; 0,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,03; -0,57</t>
+          <t>-5,19; -0,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,0</t>
+          <t>-4,15; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,0</t>
+          <t>-4,96; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,15</t>
+          <t>-0,05; 2,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,88</t>
+          <t>-1,11; 1,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 0,0</t>
+          <t>-4,22; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 0,0</t>
+          <t>-3,94; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,55</t>
+          <t>-0,28; 0,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,28</t>
+          <t>-0,75; 0,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-89,62; 157,12</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1005-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1005-Clase-trans_bre.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,71</t>
+          <t>0,0; 3,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,96</t>
+          <t>-2,76; 0,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,19; -0,57</t>
+          <t>-5,08; -0,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 0,0</t>
+          <t>-3,9; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 0,0</t>
+          <t>-5,68; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,14</t>
+          <t>-0,18; 2,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,86</t>
+          <t>-1,1; 1,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,0</t>
+          <t>-4,18; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 0,0</t>
+          <t>-4,65; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,4</t>
+          <t>-0,38; 0,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,53</t>
+          <t>-0,29; 0,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,31</t>
+          <t>-0,79; 0,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,8; 209,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1005-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1005-Clase-trans_bre.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>0,0; 4,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 0,97</t>
+          <t>-2,78; 0,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,08; -0,57</t>
+          <t>-5,03; -0,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -799,12 +799,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,0</t>
+          <t>-3,89; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 0,0</t>
+          <t>-4,47; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,13</t>
+          <t>-0,11; 2,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,94</t>
+          <t>-1,1; 1,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 0,0</t>
+          <t>-4,87; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 0,0</t>
+          <t>-4,03; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,41</t>
+          <t>-0,37; 0,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,49</t>
+          <t>-0,28; 0,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,31</t>
+          <t>-0,8; 0,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-90,8; 209,83</t>
+          <t>-89,62; 157,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1005-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1005-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,123 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.7471136331141677</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,49</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>4.491362128265158</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,22</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,86</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-31,66%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,78; 0,96</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,03; -0,57</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.2212003045155949</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.861115577330233</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="n">
+        <v>-0.3165640316753019</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,78</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,9</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="n">
+        <v>-2.783689359091629</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.034509178349494</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,89; 0,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,47; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="n">
+        <v>0.9599989163403605</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>-0.5714133414570878</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +727,137 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,32</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>298,64%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.7814190916448751</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.8972800545892317</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,61</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,9</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,11; 2,15</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
+        <v>-3.888331274013743</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.467731737700664</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,1; 1,88</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>0.3197187580737418</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.3373517609369793</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.7769836417794943</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>2.986375819788785</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-0,83</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.1098481481342453</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-4,87; 0,0</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-4,03; 0,0</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.608347806758174</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.90208865001088</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.14594196921994</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,77 +865,193 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>40,86%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-36,71%</t>
-        </is>
-      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.05692108392643131</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.1034480626378148</v>
+      </c>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,37; 0,4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,28; 0,55</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,8; 0,28</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-89,62; 157,12</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.098921489092949</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.878747796795777</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-0.8319763367449214</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-0.8088373013233169</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-4.873898490058652</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="n">
+        <v>-4.026662120736768</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.009129376610203369</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.07733838782425584</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.200275705081551</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0.0479779241221991</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.4085803131679324</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.3670750908486901</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.3688027305901971</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.2821183487529711</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.8017949433485466</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr"/>
+      <c r="H23" s="6" t="n">
+        <v>-0.8962421805970979</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.3980182189156504</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.551224922797084</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.2773794035841747</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr"/>
+      <c r="H24" s="6" t="n">
+        <v>1.571157720255523</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1153,15 +1060,15 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
